--- a/shared/words/E5_单词汇总.xlsx
+++ b/shared/words/E5_单词汇总.xlsx
@@ -1132,6 +1132,11 @@
           <t>words/einheit5/schauen.mp3</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schauen wir mal in die Speisekarte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1235,6 +1240,11 @@
           <t>words/einheit5/gefallen.mp3</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das Restaurant hier gefällt mir sehr.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1257,6 +1267,11 @@
           <t>words/einheit5/zahlen.mp3</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wir zahlen die Rechnung.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1306,6 +1321,11 @@
           <t>words/einheit5/gehören.mp3</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das Fahrrad gehört mir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1382,6 +1402,11 @@
           <t>words/einheit5/empfehlen.mp3</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Was empfehlen Sie uns?</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2403,6 +2428,11 @@
           <t>words/einheit5/Ärztin.mp3</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sie ist Ärztin.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2452,6 +2482,11 @@
           <t>words/einheit5/sonst.mp3</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Was wünschen Sie sonst noch?</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2528,6 +2563,11 @@
           <t>words/einheit5/nämlich.mp3</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich komme nämlich aus China.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2550,6 +2590,11 @@
           <t>words/einheit5/ruhig.mp3</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bestell dir ruhig eins.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2572,6 +2617,11 @@
           <t>words/einheit5/getrennt.mp3</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zahlen Sie getrennt oder zusammen?</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2594,6 +2644,11 @@
           <t>words/einheit5/sofort.mp3</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er packt das Geschenk sofort aus.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2724,6 +2779,11 @@
           <t>words/einheit5/weiß.mp3</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das Hemd ist weiß.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2746,6 +2806,11 @@
           <t>words/einheit5/beliebt.mp3</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er ist bei allen sehr beliebt.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2768,6 +2833,11 @@
           <t>words/einheit5/bekannt.mp3</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dieser Schauspieler ist bekannt.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2790,6 +2860,11 @@
           <t>words/einheit5/berühmt.mp3</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Berlin ist eine berühmte Stadt.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2812,6 +2887,11 @@
           <t>words/einheit5/fast.mp3</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich bin fast fertig.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2859,6 +2939,11 @@
       <c r="F59" t="inlineStr">
         <is>
           <t>words/einheit5/international.mp3</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist eine internationale Schule.</t>
         </is>
       </c>
     </row>
